--- a/Downloads/Splitflask-Financials/deliverables/Reconciliation_Backup.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/Reconciliation_Backup.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tax Figures Trace" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Cross-Packet Ties" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Deal GMV Trace" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Corrections &amp; Findings Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology Notes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Source Index" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -887,10 +887,10 @@
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B14:D14"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B14:D14"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B13:D13"/>
@@ -1015,7 +1015,6 @@
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" s="15" t="inlineStr">
         <is>
           <t>COGS</t>
@@ -1044,7 +1043,6 @@
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Total Deductions
@@ -1073,7 +1071,6 @@
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Net Ordinary
@@ -1138,7 +1135,6 @@
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" s="15" t="inlineStr">
         <is>
           <t>COGS</t>
@@ -1167,7 +1163,6 @@
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Total Deductions
@@ -1197,7 +1192,6 @@
       </c>
     </row>
     <row r="11" ht="90" customHeight="1">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Net Income/(Loss)</t>
@@ -1262,7 +1256,6 @@
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Total Deductions</t>
@@ -1289,7 +1282,6 @@
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Net Ordinary
@@ -1356,7 +1348,6 @@
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Total Deductions</t>
@@ -1385,7 +1376,6 @@
       </c>
     </row>
     <row r="17" ht="90" customHeight="1">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Net Income/(Loss)
@@ -1450,7 +1440,6 @@
       </c>
     </row>
     <row r="19" ht="90" customHeight="1">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Total Deductions</t>
@@ -1478,7 +1467,6 @@
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Net Income/(Loss)</t>
@@ -2456,57 +2444,55 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>CORRECTIONS &amp; MATERIAL FINDINGS LOG — 5 Discoveries That Changed the Numbers</t>
+          <t>METHODOLOGY NOTES — Data Traps Encountered &amp; How Resolved (For CPA / TJ Use)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>These findings were discovered during reconstruction. Each is documented with: what was wrong, how it was caught, and the corrected figure. This log is the credibility exhibit — showing these were found proactively, not by diligence.</t>
+          <t>These notes document known data traps in the source materials and how each was detected and corrected. Purpose: if TJ re-derives any figure from the same raw statements, these traps will recur — this log tells him they exist, their signatures, and how the reconstruction resolved them. Not for investor/buyer package — traceability is demonstrated via the source index, not narrated here.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Finding</t>
+          <t>Issue / Data Trap</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>What Was Wrong (The Bug / Error)</t>
+          <t>What the Raw Data Shows (and Why It's Misleading)</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>How It Was Caught (Detection Method)</t>
+          <t>How It Was Detected (Detection Signature)</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Impact: Before</t>
+          <t>Before Correction</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Impact: After (Corrected)</t>
+          <t>After Correction (Figures Used in Packets)</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Evidence / Source</t>
+          <t>Source Documents / Evidence</t>
         </is>
       </c>
     </row>
     <row r="4" ht="180" customHeight="1">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>Finding 1:
-WF Parser Bug
-— Running Balance
-Captured as
-Transaction Amount</t>
+          <t>Wells Fargo PDF Parser
+— Running Balance Captured
+as Transaction Amount</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
@@ -2544,11 +2530,9 @@
     <row r="5" ht="180" customHeight="1">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>Finding 2:
-The Plug Trap
-— Fees Derived as
-(1099-K minus Deposits)
-Inflated Fee Rates</t>
+          <t>Fee Plug Trap
+— 1099-K minus Deposits
+≠ Real Platform Fees</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
@@ -2592,13 +2576,9 @@
     <row r="6" ht="180" customHeight="1">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>Finding 3:
-Commingled
-QuickBooks
-Self-Employed
-Filing
+          <t>QuickBooks Commingled Filing
 — CB 2024 Schedule C
-Over-deducted ~$104K</t>
+Multiple Businesses One P&amp;L</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
@@ -2641,10 +2621,9 @@
     <row r="7" ht="180" customHeight="1">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>Finding 4:
-Facebook Invoice
-Comma-Parse Bug
-— $85,325 → Real $97,769</t>
+          <t>Facebook Invoice Comma-Parse
+— $85,325 under-parsed;
+Real Total $97,769</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
@@ -2688,11 +2667,9 @@
     <row r="8" ht="180" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Finding 5:
-2026 H1 GMV
-$430K Stale Estimate
-Caught by
-Provenance Gate</t>
+          <t>2026 H1 GMV Stale Estimate
+— $430K Estimate Not
+Source-Tied; Corrected $106K</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
